--- a/documentation/MS-ES1 instruction list.xlsx
+++ b/documentation/MS-ES1 instruction list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iacopo\Desktop\python\HBM-s-NTM-autocal-compiler-MS-ES1-\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802BE669-C51B-40B8-97CA-78A7A6F72CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E69B21D-260E-471F-89A7-FDE4AE58956D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -310,21 +310,7 @@
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill>
@@ -631,25 +617,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3C14BC2C-CAE1-47BA-A932-80DB86346411}" name="Tabella1" displayName="Tabella1" ref="A1:P33" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3C14BC2C-CAE1-47BA-A932-80DB86346411}" name="Tabella1" displayName="Tabella1" ref="A1:P33" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="A1:P33" xr:uid="{3C14BC2C-CAE1-47BA-A932-80DB86346411}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P33">
+    <sortCondition ref="C1:C33"/>
+  </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{8033F447-AEED-4C28-9994-EA7AFADD3F53}" name="N°" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{65067A3E-1A3D-49C4-A5DC-8371912B0D59}" name="Instruction" dataDxfId="20"/>
-    <tableColumn id="21" xr3:uid="{277E757C-B3CC-4038-BFCC-B2E8672B4AB2}" name="Instruction type" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{05B24E3E-CEE2-488C-951D-13B077A41D63}" name="Description" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{3AE4043C-B664-43FE-88CB-0705369C1407}" name="Buffer input" dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{5ACA0D69-BB91-4190-9DFD-1F168CDB0AD2}" name="Buffer output" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{8D726A6D-0135-48E6-ACB3-E9F391A950C2}" name="Variable substitutions" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{421E47A3-353A-402C-B876-74FE593243B5}" name="Notes" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{8931692E-206D-49D3-B928-BCD0DB883B74}" name="Colonna7" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{6000B16A-4E7D-4C3E-8833-34067FA56012}" name="Colonna8" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{29A8FED4-1C0F-419E-995D-4C41CC323340}" name="Colonna9" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{0C1C2AB3-E788-4188-BE1C-F591A90AFE18}" name="Colonna10" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{559CC935-62F2-4D8D-BBAF-32AB289F4FE2}" name="Colonna11" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{22C7E74F-B1C5-4AA0-88B6-C21C9D0C3112}" name="Colonna12" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{165E693A-25CD-49D9-BFFE-C89C2E85C7FE}" name="Colonna13" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{7BBE7D66-0D3A-41CD-83A9-846FB5F77A1A}" name="Colonna14" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{8033F447-AEED-4C28-9994-EA7AFADD3F53}" name="N°" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{65067A3E-1A3D-49C4-A5DC-8371912B0D59}" name="Instruction" dataDxfId="18"/>
+    <tableColumn id="21" xr3:uid="{277E757C-B3CC-4038-BFCC-B2E8672B4AB2}" name="Instruction type" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{05B24E3E-CEE2-488C-951D-13B077A41D63}" name="Description" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{3AE4043C-B664-43FE-88CB-0705369C1407}" name="Buffer input" dataDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{5ACA0D69-BB91-4190-9DFD-1F168CDB0AD2}" name="Buffer output" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{8D726A6D-0135-48E6-ACB3-E9F391A950C2}" name="Variable substitutions" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{421E47A3-353A-402C-B876-74FE593243B5}" name="Notes" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{8931692E-206D-49D3-B928-BCD0DB883B74}" name="Colonna7" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{6000B16A-4E7D-4C3E-8833-34067FA56012}" name="Colonna8" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{29A8FED4-1C0F-419E-995D-4C41CC323340}" name="Colonna9" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{0C1C2AB3-E788-4188-BE1C-F591A90AFE18}" name="Colonna10" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{559CC935-62F2-4D8D-BBAF-32AB289F4FE2}" name="Colonna11" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{22C7E74F-B1C5-4AA0-88B6-C21C9D0C3112}" name="Colonna12" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{165E693A-25CD-49D9-BFFE-C89C2E85C7FE}" name="Colonna13" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{7BBE7D66-0D3A-41CD-83A9-846FB5F77A1A}" name="Colonna14" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -984,72 +973,72 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="5"/>
     </row>
     <row r="3" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:16" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>20</v>
@@ -1058,232 +1047,234 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>21</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H9" s="5"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>20</v>
       </c>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
       <c r="B11" s="2" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:16" ht="63" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:16" ht="63" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>20</v>
@@ -1296,122 +1287,120 @@
       </c>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>3</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="E17" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="5" t="s">
-        <v>52</v>
-      </c>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>21</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>21</v>
@@ -1420,22 +1409,22 @@
     </row>
     <row r="20" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>21</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>21</v>
@@ -1444,46 +1433,46 @@
     </row>
     <row r="21" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>21</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>21</v>
@@ -1492,19 +1481,19 @@
     </row>
     <row r="23" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>21</v>
@@ -1514,51 +1503,51 @@
       </c>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="H24" s="5"/>
     </row>
-    <row r="25" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="H25" s="5"/>
     </row>
@@ -1628,10 +1617,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D24:F1048576 E1:G33">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
